--- a/IL_CONCETTO.xlsx
+++ b/IL_CONCETTO.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -433,7 +433,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>═══════════════════════════════════════════════════</t>
+          <t>══════════ PASSO 1 — FREQUENZA (ritorno al futuro su tutta la storia) ══════════</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -441,206 +441,216 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PASSO 1 — FREQUENZA STORICA (tutta la storia)</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
+          <t>Draw analizzati</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>7229</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>═══════════════════════════════════════════════════</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>Previsioni fatte (1 per draw, meglio di 8 strategie)</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>7229</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Draw totali analizzati</t>
+          <t>GIUSTE (4+ numeri)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7250</v>
+        <v>148</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Previsioni fatte (una per draw)</t>
+          <t>SBAGLIATE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7250</v>
+        <v>7081</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GIUSTE (4+ numeri azzeccati)</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>31</v>
+          <t>FREQUENZA R (4+ su 100 previsioni)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2.05%  -&gt;  ~2.0 ogni 100</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>SBAGLIATE</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>7219</v>
-      </c>
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Frequenza 4+</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>0.428% = 1 ogni 233.9 previsioni</t>
-        </is>
-      </c>
+          <t>══════════ PASSO 2 — LE 72 RIPETIZIONI (finestre di 100) ══════════</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Finestre con almeno 1 giusta</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>62/72</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>═══════════════════════════════════════════════════</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+          <t>Media giuste per finestra</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PASSO 2 — LE 72 RIPETIZIONI (finestre di 100)</t>
+          <t>-&gt; dettaglio nel foglio '73_Ripetizioni'</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>═══════════════════════════════════════════════════</t>
-        </is>
-      </c>
+      <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Finestre con almeno 1 hit</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>26/72</t>
-        </is>
-      </c>
+          <t>══════════ PASSO 3 — FINESTRA ATTUALE (ultime 100 fino a stasera) ══════════</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Media hit per finestra</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>0.43</t>
-        </is>
+          <t>Previsioni nella finestra</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>→ Vedi foglio '73_Ripetizioni' per il dettaglio di ogni finestra</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
+          <t>GIUSTE gia' uscite</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SBAGLIATE (le escludiamo)</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>═══════════════════════════════════════════════════</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
+          <t>ATTESE per frequenza (R x 100)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PASSO 3 — FINESTRA ATTUALE (ultime 100 previsioni che finiscono STASERA)</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
+          <t>&gt;&gt;&gt; MANCANO ANCORA ALL'APPELLO &lt;&lt;&lt;</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>═══════════════════════════════════════════════════</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
+          <t>Streak finale sbagliate consecutive</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Previsioni fatte</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>100</v>
-      </c>
+          <t>-&gt; dettaglio nel foglio 'Ultime_100'</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>SBAGLIATE (le 99 che scartiamo)</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>100</v>
-      </c>
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>GIUSTE (4+) gia' verificate</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
+          <t>══════════ PASSO 4 — STASERA (ci mettiamo nel 2%, escluso il 98%) ══════════</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Streak finale (miss consecutivi)</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>100</v>
+          <t>TOP 4 stasera</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>14 18 35 48</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>→ Vedi foglio 'Ultime_100' per il dettaglio di ogni previsione</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
+          <t>TOP 6 stasera</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>03 04 14 18 35 48</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
@@ -649,64 +659,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>═══════════════════════════════════════════════════</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>PASSO 4 — STASERA (l'ultima che manca all'appello)</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>═══════════════════════════════════════════════════</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>TOP 4 — stasera</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>14 30 36 45</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>TOP 6 — stasera</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>06 14 20 30 36 45</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>LOGICA DI ESCLUSIONE</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Su 100 previsioni nella finestra, 0 erano gia' giuste e 100 sbagliate. Le ultime 100 sono sbagliate di fila. Per esclusione, stasera e' la previsione che chiude la finestra.</t>
+          <t>LOGICA</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Su 100 previsioni la frequenza dice ~2 giuste. Nella finestra attuale ne sono uscite 4, quindi MANCANO ANCORA 0. Le ultime 18 sono sbagliate di fila: stasera e' uno dei 0 posti che restano all'appello. Numeri: 03 04 14 18 35 48.</t>
         </is>
       </c>
     </row>
@@ -721,7 +679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K73"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -742,42 +700,22 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>data_inizio</t>
+          <t>PREVISIONI</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>data_fine</t>
+          <t>SBAGLIATE</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>PREVISIONI FATTE</t>
+          <t>GIUSTE (4+)</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>SBAGLIATE</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>GIUSTE (4+)</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>pct_giuste</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
           <t>numeri_nelle_giuste</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>nota</t>
         </is>
       </c>
     </row>
@@ -786,43 +724,23 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="C2" t="n">
-        <v>200</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1959-01-18</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>1960-12-11</t>
-        </is>
+        <v>220</v>
+      </c>
+      <c r="D2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E2" t="n">
+        <v>98</v>
       </c>
       <c r="F2" t="n">
-        <v>100</v>
-      </c>
-      <c r="G2" t="n">
-        <v>100</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>(nessuna)</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>VUOTA (0 hit)</t>
+        <v>2</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>3 20 10 46</t>
         </is>
       </c>
     </row>
@@ -831,43 +749,23 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>201</v>
+        <v>221</v>
       </c>
       <c r="C3" t="n">
-        <v>300</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>1960-12-18</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>1962-11-11</t>
-        </is>
+        <v>320</v>
+      </c>
+      <c r="D3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E3" t="n">
+        <v>97</v>
       </c>
       <c r="F3" t="n">
-        <v>100</v>
-      </c>
-      <c r="G3" t="n">
-        <v>100</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>(nessuna)</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>VUOTA (0 hit)</t>
+        <v>3</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>14 8 11 12</t>
         </is>
       </c>
     </row>
@@ -876,43 +774,23 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>301</v>
+        <v>321</v>
       </c>
       <c r="C4" t="n">
-        <v>400</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>1962-11-18</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>1964-10-11</t>
-        </is>
+        <v>420</v>
+      </c>
+      <c r="D4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E4" t="n">
+        <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>100</v>
-      </c>
-      <c r="G4" t="n">
-        <v>99</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1.0%</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>6 7 22 27</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>← HA ALMENO 1</t>
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>(nessuna)</t>
         </is>
       </c>
     </row>
@@ -921,43 +799,23 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>401</v>
+        <v>421</v>
       </c>
       <c r="C5" t="n">
-        <v>500</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>1964-10-18</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>1966-08-28</t>
-        </is>
+        <v>520</v>
+      </c>
+      <c r="D5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E5" t="n">
+        <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>100</v>
-      </c>
-      <c r="G5" t="n">
-        <v>99</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1.0%</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2 29 31 38</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>← HA ALMENO 1</t>
+        <v>0</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>(nessuna)</t>
         </is>
       </c>
     </row>
@@ -966,43 +824,23 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="C6" t="n">
-        <v>600</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>1966-09-04</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>1968-07-14</t>
-        </is>
+        <v>620</v>
+      </c>
+      <c r="D6" t="n">
+        <v>100</v>
+      </c>
+      <c r="E6" t="n">
+        <v>97</v>
       </c>
       <c r="F6" t="n">
-        <v>100</v>
-      </c>
-      <c r="G6" t="n">
-        <v>100</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>(nessuna)</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>VUOTA (0 hit)</t>
+        <v>3</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>32 12 19 30</t>
         </is>
       </c>
     </row>
@@ -1011,43 +849,23 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>601</v>
+        <v>621</v>
       </c>
       <c r="C7" t="n">
-        <v>700</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>1968-07-21</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>1970-05-24</t>
-        </is>
+        <v>720</v>
+      </c>
+      <c r="D7" t="n">
+        <v>100</v>
+      </c>
+      <c r="E7" t="n">
+        <v>98</v>
       </c>
       <c r="F7" t="n">
-        <v>100</v>
-      </c>
-      <c r="G7" t="n">
-        <v>100</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>(nessuna)</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>VUOTA (0 hit)</t>
+        <v>2</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>7 17 26 32</t>
         </is>
       </c>
     </row>
@@ -1056,43 +874,23 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>701</v>
+        <v>721</v>
       </c>
       <c r="C8" t="n">
-        <v>800</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>1970-05-31</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>1972-02-20</t>
-        </is>
+        <v>820</v>
+      </c>
+      <c r="D8" t="n">
+        <v>100</v>
+      </c>
+      <c r="E8" t="n">
+        <v>100</v>
       </c>
       <c r="F8" t="n">
-        <v>100</v>
-      </c>
-      <c r="G8" t="n">
-        <v>100</v>
-      </c>
-      <c r="H8" t="n">
         <v>0</v>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>(nessuna)</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>VUOTA (0 hit)</t>
         </is>
       </c>
     </row>
@@ -1101,43 +899,23 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>801</v>
+        <v>821</v>
       </c>
       <c r="C9" t="n">
-        <v>900</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>1972-02-27</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>1973-07-15</t>
-        </is>
+        <v>920</v>
+      </c>
+      <c r="D9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" t="n">
+        <v>96</v>
       </c>
       <c r="F9" t="n">
-        <v>100</v>
-      </c>
-      <c r="G9" t="n">
-        <v>100</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>(nessuna)</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>VUOTA (0 hit)</t>
+        <v>4</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>22 3 9 44</t>
         </is>
       </c>
     </row>
@@ -1146,43 +924,23 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>901</v>
+        <v>921</v>
       </c>
       <c r="C10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>1973-07-22</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>1974-11-10</t>
-        </is>
+        <v>1020</v>
+      </c>
+      <c r="D10" t="n">
+        <v>100</v>
+      </c>
+      <c r="E10" t="n">
+        <v>97</v>
       </c>
       <c r="F10" t="n">
-        <v>100</v>
-      </c>
-      <c r="G10" t="n">
-        <v>99</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1.0%</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>1 40 42 49</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>← HA ALMENO 1</t>
+        <v>3</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>3 9 10 11</t>
         </is>
       </c>
     </row>
@@ -1191,43 +949,23 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>1001</v>
+        <v>1021</v>
       </c>
       <c r="C11" t="n">
-        <v>1100</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>1974-11-10</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>1975-10-26</t>
-        </is>
+        <v>1120</v>
+      </c>
+      <c r="D11" t="n">
+        <v>100</v>
+      </c>
+      <c r="E11" t="n">
+        <v>94</v>
       </c>
       <c r="F11" t="n">
-        <v>100</v>
-      </c>
-      <c r="G11" t="n">
-        <v>100</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>(nessuna)</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>VUOTA (0 hit)</t>
+        <v>6</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>13 39 1 23</t>
         </is>
       </c>
     </row>
@@ -1236,43 +974,23 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>1101</v>
+        <v>1121</v>
       </c>
       <c r="C12" t="n">
-        <v>1200</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>1975-10-26</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>1976-10-10</t>
-        </is>
+        <v>1220</v>
+      </c>
+      <c r="D12" t="n">
+        <v>100</v>
+      </c>
+      <c r="E12" t="n">
+        <v>98</v>
       </c>
       <c r="F12" t="n">
-        <v>100</v>
-      </c>
-      <c r="G12" t="n">
-        <v>100</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>(nessuna)</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>VUOTA (0 hit)</t>
+        <v>2</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>4 21 43 49</t>
         </is>
       </c>
     </row>
@@ -1281,43 +999,23 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>1201</v>
+        <v>1221</v>
       </c>
       <c r="C13" t="n">
-        <v>1300</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>1976-10-10</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>1977-09-25</t>
-        </is>
+        <v>1320</v>
+      </c>
+      <c r="D13" t="n">
+        <v>100</v>
+      </c>
+      <c r="E13" t="n">
+        <v>96</v>
       </c>
       <c r="F13" t="n">
-        <v>100</v>
-      </c>
-      <c r="G13" t="n">
-        <v>99</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1.0%</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>7 14 19 22</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>← HA ALMENO 1</t>
+        <v>4</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1 7 22 24</t>
         </is>
       </c>
     </row>
@@ -1326,43 +1024,23 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>1301</v>
+        <v>1321</v>
       </c>
       <c r="C14" t="n">
-        <v>1400</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>1977-09-25</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>1978-09-10</t>
-        </is>
+        <v>1420</v>
+      </c>
+      <c r="D14" t="n">
+        <v>100</v>
+      </c>
+      <c r="E14" t="n">
+        <v>98</v>
       </c>
       <c r="F14" t="n">
-        <v>100</v>
-      </c>
-      <c r="G14" t="n">
-        <v>99</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1.0%</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>7 11 23 46</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>← HA ALMENO 1</t>
+        <v>2</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>6 9 11 38</t>
         </is>
       </c>
     </row>
@@ -1371,43 +1049,23 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>1401</v>
+        <v>1421</v>
       </c>
       <c r="C15" t="n">
-        <v>1500</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>1978-09-10</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>1979-08-26</t>
-        </is>
+        <v>1520</v>
+      </c>
+      <c r="D15" t="n">
+        <v>100</v>
+      </c>
+      <c r="E15" t="n">
+        <v>98</v>
       </c>
       <c r="F15" t="n">
-        <v>100</v>
-      </c>
-      <c r="G15" t="n">
-        <v>100</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>(nessuna)</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>VUOTA (0 hit)</t>
+        <v>2</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>11 14 15 44</t>
         </is>
       </c>
     </row>
@@ -1416,43 +1074,23 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>1501</v>
+        <v>1521</v>
       </c>
       <c r="C16" t="n">
-        <v>1600</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>1979-08-26</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>1980-08-10</t>
-        </is>
+        <v>1620</v>
+      </c>
+      <c r="D16" t="n">
+        <v>100</v>
+      </c>
+      <c r="E16" t="n">
+        <v>98</v>
       </c>
       <c r="F16" t="n">
-        <v>100</v>
-      </c>
-      <c r="G16" t="n">
-        <v>100</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>(nessuna)</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>VUOTA (0 hit)</t>
+        <v>2</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>6 15 16 32</t>
         </is>
       </c>
     </row>
@@ -1461,43 +1099,23 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>1601</v>
+        <v>1621</v>
       </c>
       <c r="C17" t="n">
-        <v>1700</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>1980-08-10</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>1981-07-26</t>
-        </is>
+        <v>1720</v>
+      </c>
+      <c r="D17" t="n">
+        <v>100</v>
+      </c>
+      <c r="E17" t="n">
+        <v>98</v>
       </c>
       <c r="F17" t="n">
-        <v>100</v>
-      </c>
-      <c r="G17" t="n">
-        <v>100</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>(nessuna)</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>VUOTA (0 hit)</t>
+        <v>2</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>8 12 23 30</t>
         </is>
       </c>
     </row>
@@ -1506,43 +1124,23 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>1701</v>
+        <v>1721</v>
       </c>
       <c r="C18" t="n">
-        <v>1800</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>1981-07-26</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>1982-07-11</t>
-        </is>
+        <v>1820</v>
+      </c>
+      <c r="D18" t="n">
+        <v>100</v>
+      </c>
+      <c r="E18" t="n">
+        <v>98</v>
       </c>
       <c r="F18" t="n">
-        <v>100</v>
-      </c>
-      <c r="G18" t="n">
-        <v>100</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>(nessuna)</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>VUOTA (0 hit)</t>
+        <v>2</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>31 5 24 38</t>
         </is>
       </c>
     </row>
@@ -1551,43 +1149,23 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>1801</v>
+        <v>1821</v>
       </c>
       <c r="C19" t="n">
-        <v>1900</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>1982-07-11</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>1983-06-26</t>
-        </is>
+        <v>1920</v>
+      </c>
+      <c r="D19" t="n">
+        <v>100</v>
+      </c>
+      <c r="E19" t="n">
+        <v>98</v>
       </c>
       <c r="F19" t="n">
-        <v>100</v>
-      </c>
-      <c r="G19" t="n">
-        <v>99</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1.0%</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>9 30 35 36</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>← HA ALMENO 1</t>
+        <v>2</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>33 9 36 43</t>
         </is>
       </c>
     </row>
@@ -1596,43 +1174,23 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>1901</v>
+        <v>1921</v>
       </c>
       <c r="C20" t="n">
-        <v>2000</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>1983-06-26</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>1984-06-09</t>
-        </is>
+        <v>2020</v>
+      </c>
+      <c r="D20" t="n">
+        <v>100</v>
+      </c>
+      <c r="E20" t="n">
+        <v>100</v>
       </c>
       <c r="F20" t="n">
-        <v>100</v>
-      </c>
-      <c r="G20" t="n">
-        <v>98</v>
-      </c>
-      <c r="H20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2.0%</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>35 38 42 45</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>← HA ALMENO 1</t>
+        <v>0</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>(nessuna)</t>
         </is>
       </c>
     </row>
@@ -1641,43 +1199,23 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>2001</v>
+        <v>2021</v>
       </c>
       <c r="C21" t="n">
-        <v>2100</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>1984-06-09</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>1985-05-25</t>
-        </is>
+        <v>2120</v>
+      </c>
+      <c r="D21" t="n">
+        <v>100</v>
+      </c>
+      <c r="E21" t="n">
+        <v>97</v>
       </c>
       <c r="F21" t="n">
-        <v>100</v>
-      </c>
-      <c r="G21" t="n">
-        <v>100</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>(nessuna)</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>VUOTA (0 hit)</t>
+        <v>3</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>6 1 24 39</t>
         </is>
       </c>
     </row>
@@ -1686,43 +1224,23 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>2101</v>
+        <v>2121</v>
       </c>
       <c r="C22" t="n">
-        <v>2200</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>1985-05-25</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>1986-05-10</t>
-        </is>
+        <v>2220</v>
+      </c>
+      <c r="D22" t="n">
+        <v>100</v>
+      </c>
+      <c r="E22" t="n">
+        <v>100</v>
       </c>
       <c r="F22" t="n">
-        <v>100</v>
-      </c>
-      <c r="G22" t="n">
-        <v>100</v>
-      </c>
-      <c r="H22" t="n">
         <v>0</v>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>(nessuna)</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>VUOTA (0 hit)</t>
         </is>
       </c>
     </row>
@@ -1731,43 +1249,23 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>2201</v>
+        <v>2221</v>
       </c>
       <c r="C23" t="n">
-        <v>2300</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>1986-05-10</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>1987-04-25</t>
-        </is>
+        <v>2320</v>
+      </c>
+      <c r="D23" t="n">
+        <v>100</v>
+      </c>
+      <c r="E23" t="n">
+        <v>97</v>
       </c>
       <c r="F23" t="n">
-        <v>100</v>
-      </c>
-      <c r="G23" t="n">
-        <v>100</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>(nessuna)</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>VUOTA (0 hit)</t>
+        <v>3</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>6 1 8 21</t>
         </is>
       </c>
     </row>
@@ -1776,43 +1274,23 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>2301</v>
+        <v>2321</v>
       </c>
       <c r="C24" t="n">
-        <v>2400</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>1987-04-25</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>1988-04-09</t>
-        </is>
+        <v>2420</v>
+      </c>
+      <c r="D24" t="n">
+        <v>100</v>
+      </c>
+      <c r="E24" t="n">
+        <v>97</v>
       </c>
       <c r="F24" t="n">
-        <v>100</v>
-      </c>
-      <c r="G24" t="n">
-        <v>100</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>(nessuna)</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>VUOTA (0 hit)</t>
+        <v>3</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>8 11 17 6</t>
         </is>
       </c>
     </row>
@@ -1821,43 +1299,23 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>2401</v>
+        <v>2421</v>
       </c>
       <c r="C25" t="n">
-        <v>2500</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>1988-04-09</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>1989-03-25</t>
-        </is>
+        <v>2520</v>
+      </c>
+      <c r="D25" t="n">
+        <v>100</v>
+      </c>
+      <c r="E25" t="n">
+        <v>97</v>
       </c>
       <c r="F25" t="n">
-        <v>100</v>
-      </c>
-      <c r="G25" t="n">
-        <v>100</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>(nessuna)</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>VUOTA (0 hit)</t>
+        <v>3</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>22 16 18 24</t>
         </is>
       </c>
     </row>
@@ -1866,43 +1324,23 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>2501</v>
+        <v>2521</v>
       </c>
       <c r="C26" t="n">
-        <v>2600</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>1989-03-25</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>1990-03-10</t>
-        </is>
+        <v>2620</v>
+      </c>
+      <c r="D26" t="n">
+        <v>100</v>
+      </c>
+      <c r="E26" t="n">
+        <v>95</v>
       </c>
       <c r="F26" t="n">
-        <v>100</v>
-      </c>
-      <c r="G26" t="n">
-        <v>100</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>(nessuna)</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>VUOTA (0 hit)</t>
+        <v>5</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>10 28 17 24</t>
         </is>
       </c>
     </row>
@@ -1911,43 +1349,23 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>2601</v>
+        <v>2621</v>
       </c>
       <c r="C27" t="n">
-        <v>2700</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>1990-03-10</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>1991-02-23</t>
-        </is>
+        <v>2720</v>
+      </c>
+      <c r="D27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E27" t="n">
+        <v>100</v>
       </c>
       <c r="F27" t="n">
-        <v>100</v>
-      </c>
-      <c r="G27" t="n">
-        <v>100</v>
-      </c>
-      <c r="H27" t="n">
         <v>0</v>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>(nessuna)</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>VUOTA (0 hit)</t>
         </is>
       </c>
     </row>
@@ -1956,43 +1374,23 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>2701</v>
+        <v>2721</v>
       </c>
       <c r="C28" t="n">
-        <v>2800</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>1991-02-23</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>1992-02-05</t>
-        </is>
+        <v>2820</v>
+      </c>
+      <c r="D28" t="n">
+        <v>100</v>
+      </c>
+      <c r="E28" t="n">
+        <v>96</v>
       </c>
       <c r="F28" t="n">
-        <v>100</v>
-      </c>
-      <c r="G28" t="n">
-        <v>100</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>(nessuna)</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>VUOTA (0 hit)</t>
+        <v>4</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>11 27 30 37</t>
         </is>
       </c>
     </row>
@@ -2001,43 +1399,23 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>2801</v>
+        <v>2821</v>
       </c>
       <c r="C29" t="n">
-        <v>2900</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>1992-02-08</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>1993-01-20</t>
-        </is>
+        <v>2920</v>
+      </c>
+      <c r="D29" t="n">
+        <v>100</v>
+      </c>
+      <c r="E29" t="n">
+        <v>99</v>
       </c>
       <c r="F29" t="n">
-        <v>100</v>
-      </c>
-      <c r="G29" t="n">
-        <v>99</v>
-      </c>
-      <c r="H29" t="n">
         <v>1</v>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1.0%</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>7 26 32 37</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>← HA ALMENO 1</t>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2 11 15 34</t>
         </is>
       </c>
     </row>
@@ -2046,43 +1424,23 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>2901</v>
+        <v>2921</v>
       </c>
       <c r="C30" t="n">
-        <v>3000</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>1993-01-23</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>1994-01-05</t>
-        </is>
+        <v>3020</v>
+      </c>
+      <c r="D30" t="n">
+        <v>100</v>
+      </c>
+      <c r="E30" t="n">
+        <v>99</v>
       </c>
       <c r="F30" t="n">
-        <v>100</v>
-      </c>
-      <c r="G30" t="n">
-        <v>100</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>(nessuna)</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>VUOTA (0 hit)</t>
+        <v>1</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>17 27 29 47</t>
         </is>
       </c>
     </row>
@@ -2091,43 +1449,23 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>3001</v>
+        <v>3021</v>
       </c>
       <c r="C31" t="n">
-        <v>3100</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>1994-01-08</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>1994-12-21</t>
-        </is>
+        <v>3120</v>
+      </c>
+      <c r="D31" t="n">
+        <v>100</v>
+      </c>
+      <c r="E31" t="n">
+        <v>97</v>
       </c>
       <c r="F31" t="n">
-        <v>100</v>
-      </c>
-      <c r="G31" t="n">
-        <v>100</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>(nessuna)</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>VUOTA (0 hit)</t>
+        <v>3</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>15 40 21 48</t>
         </is>
       </c>
     </row>
@@ -2136,43 +1474,23 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>3101</v>
+        <v>3121</v>
       </c>
       <c r="C32" t="n">
-        <v>3200</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>1994-12-24</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>1995-12-06</t>
-        </is>
+        <v>3220</v>
+      </c>
+      <c r="D32" t="n">
+        <v>100</v>
+      </c>
+      <c r="E32" t="n">
+        <v>99</v>
       </c>
       <c r="F32" t="n">
-        <v>100</v>
-      </c>
-      <c r="G32" t="n">
-        <v>99</v>
-      </c>
-      <c r="H32" t="n">
         <v>1</v>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1.0%</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>3 21 23 41</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>← HA ALMENO 1</t>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>24 29 32 48</t>
         </is>
       </c>
     </row>
@@ -2181,43 +1499,23 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>3201</v>
+        <v>3221</v>
       </c>
       <c r="C33" t="n">
-        <v>3300</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>1995-12-09</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>1996-11-20</t>
-        </is>
+        <v>3320</v>
+      </c>
+      <c r="D33" t="n">
+        <v>100</v>
+      </c>
+      <c r="E33" t="n">
+        <v>98</v>
       </c>
       <c r="F33" t="n">
-        <v>100</v>
-      </c>
-      <c r="G33" t="n">
-        <v>100</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>(nessuna)</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>VUOTA (0 hit)</t>
+        <v>2</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>5 17 25 37</t>
         </is>
       </c>
     </row>
@@ -2226,43 +1524,23 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>3301</v>
+        <v>3321</v>
       </c>
       <c r="C34" t="n">
-        <v>3400</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>1996-11-23</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>1997-11-05</t>
-        </is>
+        <v>3420</v>
+      </c>
+      <c r="D34" t="n">
+        <v>100</v>
+      </c>
+      <c r="E34" t="n">
+        <v>99</v>
       </c>
       <c r="F34" t="n">
-        <v>100</v>
-      </c>
-      <c r="G34" t="n">
-        <v>99</v>
-      </c>
-      <c r="H34" t="n">
         <v>1</v>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1.0%</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>2 20 29 31</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>← HA ALMENO 1</t>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>5 8 31 44</t>
         </is>
       </c>
     </row>
@@ -2271,43 +1549,23 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>3401</v>
+        <v>3421</v>
       </c>
       <c r="C35" t="n">
-        <v>3500</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>1997-11-08</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>1998-10-21</t>
-        </is>
+        <v>3520</v>
+      </c>
+      <c r="D35" t="n">
+        <v>100</v>
+      </c>
+      <c r="E35" t="n">
+        <v>98</v>
       </c>
       <c r="F35" t="n">
-        <v>100</v>
-      </c>
-      <c r="G35" t="n">
-        <v>98</v>
-      </c>
-      <c r="H35" t="n">
         <v>2</v>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2.0%</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>32 8 19 22</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>← HA ALMENO 1</t>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>3 5 9 10</t>
         </is>
       </c>
     </row>
@@ -2316,43 +1574,23 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>3501</v>
+        <v>3521</v>
       </c>
       <c r="C36" t="n">
-        <v>3600</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>1998-10-24</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>1999-10-06</t>
-        </is>
+        <v>3620</v>
+      </c>
+      <c r="D36" t="n">
+        <v>100</v>
+      </c>
+      <c r="E36" t="n">
+        <v>97</v>
       </c>
       <c r="F36" t="n">
-        <v>100</v>
-      </c>
-      <c r="G36" t="n">
-        <v>99</v>
-      </c>
-      <c r="H36" t="n">
-        <v>1</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1.0%</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>1 21 23 34</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>← HA ALMENO 1</t>
+        <v>3</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>8 1 15 21</t>
         </is>
       </c>
     </row>
@@ -2361,43 +1599,23 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>3601</v>
+        <v>3621</v>
       </c>
       <c r="C37" t="n">
-        <v>3700</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>1999-10-09</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>2000-09-20</t>
-        </is>
+        <v>3720</v>
+      </c>
+      <c r="D37" t="n">
+        <v>100</v>
+      </c>
+      <c r="E37" t="n">
+        <v>99</v>
       </c>
       <c r="F37" t="n">
-        <v>100</v>
-      </c>
-      <c r="G37" t="n">
-        <v>100</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>(nessuna)</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>VUOTA (0 hit)</t>
+        <v>1</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>5 6 11 32</t>
         </is>
       </c>
     </row>
@@ -2406,43 +1624,23 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>3701</v>
+        <v>3721</v>
       </c>
       <c r="C38" t="n">
-        <v>3800</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>2000-09-23</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>2001-09-05</t>
-        </is>
+        <v>3820</v>
+      </c>
+      <c r="D38" t="n">
+        <v>100</v>
+      </c>
+      <c r="E38" t="n">
+        <v>99</v>
       </c>
       <c r="F38" t="n">
-        <v>100</v>
-      </c>
-      <c r="G38" t="n">
-        <v>100</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>(nessuna)</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>VUOTA (0 hit)</t>
+        <v>1</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>16 34 35 46</t>
         </is>
       </c>
     </row>
@@ -2451,43 +1649,23 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>3801</v>
+        <v>3821</v>
       </c>
       <c r="C39" t="n">
-        <v>3900</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>2001-09-08</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>2002-08-21</t>
-        </is>
+        <v>3920</v>
+      </c>
+      <c r="D39" t="n">
+        <v>100</v>
+      </c>
+      <c r="E39" t="n">
+        <v>97</v>
       </c>
       <c r="F39" t="n">
-        <v>100</v>
-      </c>
-      <c r="G39" t="n">
-        <v>98</v>
-      </c>
-      <c r="H39" t="n">
-        <v>2</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2.0%</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>9 33 34 36</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>← HA ALMENO 1</t>
+        <v>3</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>22 31 10 32</t>
         </is>
       </c>
     </row>
@@ -2496,43 +1674,23 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>3901</v>
+        <v>3921</v>
       </c>
       <c r="C40" t="n">
-        <v>4000</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>2002-08-24</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>2003-08-06</t>
-        </is>
+        <v>4020</v>
+      </c>
+      <c r="D40" t="n">
+        <v>100</v>
+      </c>
+      <c r="E40" t="n">
+        <v>98</v>
       </c>
       <c r="F40" t="n">
-        <v>100</v>
-      </c>
-      <c r="G40" t="n">
-        <v>99</v>
-      </c>
-      <c r="H40" t="n">
-        <v>1</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1.0%</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>4 16 26 39</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>← HA ALMENO 1</t>
+        <v>2</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2 5 44 16</t>
         </is>
       </c>
     </row>
@@ -2541,43 +1699,23 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>4001</v>
+        <v>4021</v>
       </c>
       <c r="C41" t="n">
-        <v>4100</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>2003-08-09</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>2004-07-21</t>
-        </is>
+        <v>4120</v>
+      </c>
+      <c r="D41" t="n">
+        <v>100</v>
+      </c>
+      <c r="E41" t="n">
+        <v>98</v>
       </c>
       <c r="F41" t="n">
-        <v>100</v>
-      </c>
-      <c r="G41" t="n">
-        <v>99</v>
-      </c>
-      <c r="H41" t="n">
-        <v>1</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1.0%</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>2 6 18 28</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>← HA ALMENO 1</t>
+        <v>2</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>39 4 22 47</t>
         </is>
       </c>
     </row>
@@ -2586,43 +1724,23 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>4101</v>
+        <v>4121</v>
       </c>
       <c r="C42" t="n">
-        <v>4200</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>2004-07-24</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>2005-07-06</t>
-        </is>
+        <v>4220</v>
+      </c>
+      <c r="D42" t="n">
+        <v>100</v>
+      </c>
+      <c r="E42" t="n">
+        <v>99</v>
       </c>
       <c r="F42" t="n">
-        <v>100</v>
-      </c>
-      <c r="G42" t="n">
-        <v>100</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>(nessuna)</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>VUOTA (0 hit)</t>
+        <v>1</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>20 32 43 47</t>
         </is>
       </c>
     </row>
@@ -2631,43 +1749,23 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>4201</v>
+        <v>4221</v>
       </c>
       <c r="C43" t="n">
-        <v>4300</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>2005-07-09</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>2006-06-21</t>
-        </is>
+        <v>4320</v>
+      </c>
+      <c r="D43" t="n">
+        <v>100</v>
+      </c>
+      <c r="E43" t="n">
+        <v>97</v>
       </c>
       <c r="F43" t="n">
-        <v>100</v>
-      </c>
-      <c r="G43" t="n">
-        <v>100</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>(nessuna)</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>VUOTA (0 hit)</t>
+        <v>3</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>19 38 40 49</t>
         </is>
       </c>
     </row>
@@ -2676,43 +1774,23 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>4301</v>
+        <v>4321</v>
       </c>
       <c r="C44" t="n">
-        <v>4400</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>2006-06-24</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>2007-06-06</t>
-        </is>
+        <v>4420</v>
+      </c>
+      <c r="D44" t="n">
+        <v>100</v>
+      </c>
+      <c r="E44" t="n">
+        <v>98</v>
       </c>
       <c r="F44" t="n">
-        <v>100</v>
-      </c>
-      <c r="G44" t="n">
-        <v>99</v>
-      </c>
-      <c r="H44" t="n">
-        <v>1</v>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1.0%</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>4 19 21 36</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>← HA ALMENO 1</t>
+        <v>2</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2 10 16 44</t>
         </is>
       </c>
     </row>
@@ -2721,43 +1799,23 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>4401</v>
+        <v>4421</v>
       </c>
       <c r="C45" t="n">
-        <v>4500</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>2007-06-09</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>2008-02-23</t>
-        </is>
+        <v>4520</v>
+      </c>
+      <c r="D45" t="n">
+        <v>100</v>
+      </c>
+      <c r="E45" t="n">
+        <v>96</v>
       </c>
       <c r="F45" t="n">
-        <v>100</v>
-      </c>
-      <c r="G45" t="n">
-        <v>98</v>
-      </c>
-      <c r="H45" t="n">
-        <v>2</v>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2.0%</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>43 4 21 47</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>← HA ALMENO 1</t>
+        <v>4</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>16 20 31 4</t>
         </is>
       </c>
     </row>
@@ -2766,43 +1824,23 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>4501</v>
+        <v>4521</v>
       </c>
       <c r="C46" t="n">
-        <v>4600</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>2008-02-26</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>2008-10-14</t>
-        </is>
+        <v>4620</v>
+      </c>
+      <c r="D46" t="n">
+        <v>100</v>
+      </c>
+      <c r="E46" t="n">
+        <v>99</v>
       </c>
       <c r="F46" t="n">
-        <v>100</v>
-      </c>
-      <c r="G46" t="n">
-        <v>100</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>(nessuna)</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>VUOTA (0 hit)</t>
+        <v>1</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>11 26 32 48</t>
         </is>
       </c>
     </row>
@@ -2811,43 +1849,23 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>4601</v>
+        <v>4621</v>
       </c>
       <c r="C47" t="n">
-        <v>4700</v>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>2008-10-16</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>2009-06-04</t>
-        </is>
+        <v>4720</v>
+      </c>
+      <c r="D47" t="n">
+        <v>100</v>
+      </c>
+      <c r="E47" t="n">
+        <v>96</v>
       </c>
       <c r="F47" t="n">
-        <v>100</v>
-      </c>
-      <c r="G47" t="n">
-        <v>99</v>
-      </c>
-      <c r="H47" t="n">
-        <v>1</v>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1.0%</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>6 40 45 49</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>← HA ALMENO 1</t>
+        <v>4</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>40 17 18 45</t>
         </is>
       </c>
     </row>
@@ -2856,43 +1874,23 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>4701</v>
+        <v>4721</v>
       </c>
       <c r="C48" t="n">
-        <v>4800</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>2009-06-06</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>2010-01-23</t>
-        </is>
+        <v>4820</v>
+      </c>
+      <c r="D48" t="n">
+        <v>100</v>
+      </c>
+      <c r="E48" t="n">
+        <v>97</v>
       </c>
       <c r="F48" t="n">
-        <v>100</v>
-      </c>
-      <c r="G48" t="n">
-        <v>100</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>(nessuna)</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>VUOTA (0 hit)</t>
+        <v>3</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>4 27 3 9</t>
         </is>
       </c>
     </row>
@@ -2901,43 +1899,23 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>4801</v>
+        <v>4821</v>
       </c>
       <c r="C49" t="n">
-        <v>4900</v>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>2010-01-26</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>2010-09-14</t>
-        </is>
+        <v>4920</v>
+      </c>
+      <c r="D49" t="n">
+        <v>100</v>
+      </c>
+      <c r="E49" t="n">
+        <v>96</v>
       </c>
       <c r="F49" t="n">
-        <v>100</v>
-      </c>
-      <c r="G49" t="n">
-        <v>98</v>
-      </c>
-      <c r="H49" t="n">
-        <v>2</v>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>2.0%</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>7 4 11 39</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>← HA ALMENO 1</t>
+        <v>4</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2 23 1 49</t>
         </is>
       </c>
     </row>
@@ -2946,43 +1924,23 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>4901</v>
+        <v>4921</v>
       </c>
       <c r="C50" t="n">
-        <v>5000</v>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>2010-09-16</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>2011-05-05</t>
-        </is>
+        <v>5020</v>
+      </c>
+      <c r="D50" t="n">
+        <v>100</v>
+      </c>
+      <c r="E50" t="n">
+        <v>99</v>
       </c>
       <c r="F50" t="n">
-        <v>100</v>
-      </c>
-      <c r="G50" t="n">
-        <v>100</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>(nessuna)</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>VUOTA (0 hit)</t>
+        <v>1</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>19 21 33 45</t>
         </is>
       </c>
     </row>
@@ -2991,43 +1949,23 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>5001</v>
+        <v>5021</v>
       </c>
       <c r="C51" t="n">
-        <v>5100</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>2011-05-07</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>2011-12-24</t>
-        </is>
+        <v>5120</v>
+      </c>
+      <c r="D51" t="n">
+        <v>100</v>
+      </c>
+      <c r="E51" t="n">
+        <v>99</v>
       </c>
       <c r="F51" t="n">
-        <v>100</v>
-      </c>
-      <c r="G51" t="n">
-        <v>100</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>(nessuna)</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>VUOTA (0 hit)</t>
+        <v>1</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2 5 18 46</t>
         </is>
       </c>
     </row>
@@ -3036,43 +1974,23 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>5101</v>
+        <v>5121</v>
       </c>
       <c r="C52" t="n">
-        <v>5200</v>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>2011-12-27</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>2012-08-14</t>
-        </is>
+        <v>5220</v>
+      </c>
+      <c r="D52" t="n">
+        <v>100</v>
+      </c>
+      <c r="E52" t="n">
+        <v>96</v>
       </c>
       <c r="F52" t="n">
-        <v>100</v>
-      </c>
-      <c r="G52" t="n">
-        <v>99</v>
-      </c>
-      <c r="H52" t="n">
-        <v>1</v>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1.0%</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>6 9 13 29</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>← HA ALMENO 1</t>
+        <v>4</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>6 8 29 33</t>
         </is>
       </c>
     </row>
@@ -3081,43 +1999,23 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>5201</v>
+        <v>5221</v>
       </c>
       <c r="C53" t="n">
-        <v>5300</v>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>2012-08-16</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>2013-04-04</t>
-        </is>
+        <v>5320</v>
+      </c>
+      <c r="D53" t="n">
+        <v>100</v>
+      </c>
+      <c r="E53" t="n">
+        <v>98</v>
       </c>
       <c r="F53" t="n">
-        <v>100</v>
-      </c>
-      <c r="G53" t="n">
-        <v>100</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>(nessuna)</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>VUOTA (0 hit)</t>
+        <v>2</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>25 28 33 35</t>
         </is>
       </c>
     </row>
@@ -3126,43 +2024,23 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>5301</v>
+        <v>5321</v>
       </c>
       <c r="C54" t="n">
-        <v>5400</v>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>2013-04-06</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>2013-11-23</t>
-        </is>
+        <v>5420</v>
+      </c>
+      <c r="D54" t="n">
+        <v>100</v>
+      </c>
+      <c r="E54" t="n">
+        <v>98</v>
       </c>
       <c r="F54" t="n">
-        <v>100</v>
-      </c>
-      <c r="G54" t="n">
-        <v>100</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>(nessuna)</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>VUOTA (0 hit)</t>
+        <v>2</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>3 10 35 37</t>
         </is>
       </c>
     </row>
@@ -3171,43 +2049,23 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>5401</v>
+        <v>5421</v>
       </c>
       <c r="C55" t="n">
-        <v>5500</v>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>2013-11-26</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>2014-07-15</t>
-        </is>
+        <v>5520</v>
+      </c>
+      <c r="D55" t="n">
+        <v>100</v>
+      </c>
+      <c r="E55" t="n">
+        <v>100</v>
       </c>
       <c r="F55" t="n">
-        <v>100</v>
-      </c>
-      <c r="G55" t="n">
-        <v>100</v>
-      </c>
-      <c r="H55" t="n">
         <v>0</v>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>(nessuna)</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>VUOTA (0 hit)</t>
         </is>
       </c>
     </row>
@@ -3216,43 +2074,23 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>5501</v>
+        <v>5521</v>
       </c>
       <c r="C56" t="n">
-        <v>5600</v>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>2014-07-17</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>2015-03-05</t>
-        </is>
+        <v>5620</v>
+      </c>
+      <c r="D56" t="n">
+        <v>100</v>
+      </c>
+      <c r="E56" t="n">
+        <v>99</v>
       </c>
       <c r="F56" t="n">
-        <v>100</v>
-      </c>
-      <c r="G56" t="n">
-        <v>99</v>
-      </c>
-      <c r="H56" t="n">
         <v>1</v>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1.0%</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>11 19 20 40</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>← HA ALMENO 1</t>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2 10 19 44</t>
         </is>
       </c>
     </row>
@@ -3261,43 +2099,23 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>5601</v>
+        <v>5621</v>
       </c>
       <c r="C57" t="n">
-        <v>5700</v>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>2015-03-07</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>2015-10-24</t>
-        </is>
+        <v>5720</v>
+      </c>
+      <c r="D57" t="n">
+        <v>100</v>
+      </c>
+      <c r="E57" t="n">
+        <v>98</v>
       </c>
       <c r="F57" t="n">
-        <v>100</v>
-      </c>
-      <c r="G57" t="n">
-        <v>100</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>(nessuna)</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>VUOTA (0 hit)</t>
+        <v>2</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>8 7 10 12</t>
         </is>
       </c>
     </row>
@@ -3306,43 +2124,23 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>5701</v>
+        <v>5721</v>
       </c>
       <c r="C58" t="n">
-        <v>5800</v>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>2015-10-27</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>2016-06-14</t>
-        </is>
+        <v>5820</v>
+      </c>
+      <c r="D58" t="n">
+        <v>100</v>
+      </c>
+      <c r="E58" t="n">
+        <v>99</v>
       </c>
       <c r="F58" t="n">
-        <v>100</v>
-      </c>
-      <c r="G58" t="n">
-        <v>99</v>
-      </c>
-      <c r="H58" t="n">
         <v>1</v>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1.0%</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>4 7 41 48</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>← HA ALMENO 1</t>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>24 31 34 36</t>
         </is>
       </c>
     </row>
@@ -3351,43 +2149,23 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>5801</v>
+        <v>5821</v>
       </c>
       <c r="C59" t="n">
-        <v>5900</v>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>2016-06-16</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>2017-02-02</t>
-        </is>
+        <v>5920</v>
+      </c>
+      <c r="D59" t="n">
+        <v>100</v>
+      </c>
+      <c r="E59" t="n">
+        <v>100</v>
       </c>
       <c r="F59" t="n">
-        <v>100</v>
-      </c>
-      <c r="G59" t="n">
-        <v>100</v>
-      </c>
-      <c r="H59" t="n">
         <v>0</v>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>(nessuna)</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>VUOTA (0 hit)</t>
         </is>
       </c>
     </row>
@@ -3396,43 +2174,23 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>5901</v>
+        <v>5921</v>
       </c>
       <c r="C60" t="n">
-        <v>6000</v>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>2017-02-04</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>2017-09-23</t>
-        </is>
+        <v>6020</v>
+      </c>
+      <c r="D60" t="n">
+        <v>100</v>
+      </c>
+      <c r="E60" t="n">
+        <v>100</v>
       </c>
       <c r="F60" t="n">
-        <v>100</v>
-      </c>
-      <c r="G60" t="n">
-        <v>100</v>
-      </c>
-      <c r="H60" t="n">
         <v>0</v>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>(nessuna)</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>VUOTA (0 hit)</t>
         </is>
       </c>
     </row>
@@ -3441,43 +2199,23 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>6001</v>
+        <v>6021</v>
       </c>
       <c r="C61" t="n">
-        <v>6100</v>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>2017-09-26</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>2018-05-15</t>
-        </is>
+        <v>6120</v>
+      </c>
+      <c r="D61" t="n">
+        <v>100</v>
+      </c>
+      <c r="E61" t="n">
+        <v>97</v>
       </c>
       <c r="F61" t="n">
-        <v>100</v>
-      </c>
-      <c r="G61" t="n">
-        <v>100</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>(nessuna)</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>VUOTA (0 hit)</t>
+        <v>3</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>34 6 14 30</t>
         </is>
       </c>
     </row>
@@ -3486,43 +2224,23 @@
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>6101</v>
+        <v>6121</v>
       </c>
       <c r="C62" t="n">
-        <v>6200</v>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>2018-05-17</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>2019-01-03</t>
-        </is>
+        <v>6220</v>
+      </c>
+      <c r="D62" t="n">
+        <v>100</v>
+      </c>
+      <c r="E62" t="n">
+        <v>100</v>
       </c>
       <c r="F62" t="n">
-        <v>100</v>
-      </c>
-      <c r="G62" t="n">
-        <v>100</v>
-      </c>
-      <c r="H62" t="n">
         <v>0</v>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>(nessuna)</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>VUOTA (0 hit)</t>
         </is>
       </c>
     </row>
@@ -3531,43 +2249,23 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>6201</v>
+        <v>6221</v>
       </c>
       <c r="C63" t="n">
-        <v>6300</v>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>2019-01-05</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>2019-08-24</t>
-        </is>
+        <v>6320</v>
+      </c>
+      <c r="D63" t="n">
+        <v>100</v>
+      </c>
+      <c r="E63" t="n">
+        <v>98</v>
       </c>
       <c r="F63" t="n">
-        <v>100</v>
-      </c>
-      <c r="G63" t="n">
-        <v>100</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>(nessuna)</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>VUOTA (0 hit)</t>
+        <v>2</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>41 8 11 20</t>
         </is>
       </c>
     </row>
@@ -3576,43 +2274,23 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>6301</v>
+        <v>6321</v>
       </c>
       <c r="C64" t="n">
-        <v>6400</v>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>2019-08-27</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>2020-04-14</t>
-        </is>
+        <v>6420</v>
+      </c>
+      <c r="D64" t="n">
+        <v>100</v>
+      </c>
+      <c r="E64" t="n">
+        <v>97</v>
       </c>
       <c r="F64" t="n">
-        <v>100</v>
-      </c>
-      <c r="G64" t="n">
-        <v>99</v>
-      </c>
-      <c r="H64" t="n">
-        <v>1</v>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>1.0%</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>10 27 35 40</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>← HA ALMENO 1</t>
+        <v>3</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>36 21 37 44</t>
         </is>
       </c>
     </row>
@@ -3621,43 +2299,23 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>6401</v>
+        <v>6421</v>
       </c>
       <c r="C65" t="n">
-        <v>6500</v>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>2020-04-16</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>2020-12-03</t>
-        </is>
+        <v>6520</v>
+      </c>
+      <c r="D65" t="n">
+        <v>100</v>
+      </c>
+      <c r="E65" t="n">
+        <v>98</v>
       </c>
       <c r="F65" t="n">
-        <v>100</v>
-      </c>
-      <c r="G65" t="n">
-        <v>99</v>
-      </c>
-      <c r="H65" t="n">
-        <v>1</v>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>1.0%</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>10 15 16 19</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>← HA ALMENO 1</t>
+        <v>2</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>42 29 31 33</t>
         </is>
       </c>
     </row>
@@ -3666,43 +2324,23 @@
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>6501</v>
+        <v>6521</v>
       </c>
       <c r="C66" t="n">
-        <v>6600</v>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>2020-12-05</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>2021-07-24</t>
-        </is>
+        <v>6620</v>
+      </c>
+      <c r="D66" t="n">
+        <v>100</v>
+      </c>
+      <c r="E66" t="n">
+        <v>99</v>
       </c>
       <c r="F66" t="n">
-        <v>100</v>
-      </c>
-      <c r="G66" t="n">
-        <v>100</v>
-      </c>
-      <c r="H66" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>(nessuna)</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>VUOTA (0 hit)</t>
+        <v>1</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>7 12 35 46</t>
         </is>
       </c>
     </row>
@@ -3711,43 +2349,23 @@
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>6601</v>
+        <v>6621</v>
       </c>
       <c r="C67" t="n">
-        <v>6700</v>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>2021-07-27</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>2022-03-15</t>
-        </is>
+        <v>6720</v>
+      </c>
+      <c r="D67" t="n">
+        <v>100</v>
+      </c>
+      <c r="E67" t="n">
+        <v>99</v>
       </c>
       <c r="F67" t="n">
-        <v>100</v>
-      </c>
-      <c r="G67" t="n">
-        <v>100</v>
-      </c>
-      <c r="H67" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>(nessuna)</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>VUOTA (0 hit)</t>
+        <v>1</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>6 9 12 40</t>
         </is>
       </c>
     </row>
@@ -3756,43 +2374,23 @@
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>6701</v>
+        <v>6721</v>
       </c>
       <c r="C68" t="n">
-        <v>6800</v>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>2022-03-17</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>2022-11-03</t>
-        </is>
+        <v>6820</v>
+      </c>
+      <c r="D68" t="n">
+        <v>100</v>
+      </c>
+      <c r="E68" t="n">
+        <v>97</v>
       </c>
       <c r="F68" t="n">
-        <v>100</v>
-      </c>
-      <c r="G68" t="n">
-        <v>100</v>
-      </c>
-      <c r="H68" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>(nessuna)</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>VUOTA (0 hit)</t>
+        <v>3</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>49 12 14 21</t>
         </is>
       </c>
     </row>
@@ -3801,43 +2399,23 @@
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>6801</v>
+        <v>6821</v>
       </c>
       <c r="C69" t="n">
-        <v>6900</v>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>2023-06-24</t>
-        </is>
+        <v>6920</v>
+      </c>
+      <c r="D69" t="n">
+        <v>100</v>
+      </c>
+      <c r="E69" t="n">
+        <v>97</v>
       </c>
       <c r="F69" t="n">
-        <v>100</v>
-      </c>
-      <c r="G69" t="n">
-        <v>100</v>
-      </c>
-      <c r="H69" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>(nessuna)</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>VUOTA (0 hit)</t>
+        <v>3</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>48 12 17 25</t>
         </is>
       </c>
     </row>
@@ -3846,43 +2424,23 @@
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>6901</v>
+        <v>6921</v>
       </c>
       <c r="C70" t="n">
-        <v>7000</v>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>2023-06-27</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>2024-02-13</t>
-        </is>
+        <v>7020</v>
+      </c>
+      <c r="D70" t="n">
+        <v>100</v>
+      </c>
+      <c r="E70" t="n">
+        <v>98</v>
       </c>
       <c r="F70" t="n">
-        <v>100</v>
-      </c>
-      <c r="G70" t="n">
-        <v>99</v>
-      </c>
-      <c r="H70" t="n">
-        <v>1</v>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1.0%</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>5 7 17 31</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>← HA ALMENO 1</t>
+        <v>2</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>5 44 1 11</t>
         </is>
       </c>
     </row>
@@ -3891,43 +2449,23 @@
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>7001</v>
+        <v>7021</v>
       </c>
       <c r="C71" t="n">
-        <v>7100</v>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>2024-02-15</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>2024-10-03</t>
-        </is>
+        <v>7120</v>
+      </c>
+      <c r="D71" t="n">
+        <v>100</v>
+      </c>
+      <c r="E71" t="n">
+        <v>98</v>
       </c>
       <c r="F71" t="n">
-        <v>100</v>
-      </c>
-      <c r="G71" t="n">
-        <v>99</v>
-      </c>
-      <c r="H71" t="n">
-        <v>1</v>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>1.0%</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>2 12 17 21</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>← HA ALMENO 1</t>
+        <v>2</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>6 25 29 31</t>
         </is>
       </c>
     </row>
@@ -3936,43 +2474,23 @@
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>7101</v>
+        <v>7121</v>
       </c>
       <c r="C72" t="n">
-        <v>7200</v>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>2024-10-05</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>2025-05-24</t>
-        </is>
+        <v>7220</v>
+      </c>
+      <c r="D72" t="n">
+        <v>100</v>
+      </c>
+      <c r="E72" t="n">
+        <v>99</v>
       </c>
       <c r="F72" t="n">
-        <v>100</v>
-      </c>
-      <c r="G72" t="n">
-        <v>100</v>
-      </c>
-      <c r="H72" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>(nessuna)</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>VUOTA (0 hit)</t>
+        <v>1</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>2 15 19 25</t>
         </is>
       </c>
     </row>
@@ -3981,43 +2499,23 @@
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>7201</v>
+        <v>7221</v>
       </c>
       <c r="C73" t="n">
-        <v>7300</v>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>2026-01-13</t>
-        </is>
+        <v>7320</v>
+      </c>
+      <c r="D73" t="n">
+        <v>100</v>
+      </c>
+      <c r="E73" t="n">
+        <v>97</v>
       </c>
       <c r="F73" t="n">
-        <v>100</v>
-      </c>
-      <c r="G73" t="n">
-        <v>100</v>
-      </c>
-      <c r="H73" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>(nessuna)</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>VUOTA (0 hit)</t>
+        <v>3</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>16 4 13 47</t>
         </is>
       </c>
     </row>
@@ -4032,13 +2530,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I102"/>
+  <dimension ref="A1:H102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>posizione_globale</t>
+          <t>n_in_finestra</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -4048,12 +2546,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>previsione_8</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>previsione_8</t>
+          <t>strategia_migliore</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -4074,39 +2572,34 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>esito_4plus</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>n_previsione_in_finestra</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7251</v>
+        <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>7251</v>
+        <v>7250</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>10 17 20 28 30 36 46 49</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>05 06 10 17 20 24 30 49</t>
+          <t>FreqHot8</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>05 09 11 14 35 36</t>
+          <t>06 15 20 24 34 43</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -4117,74 +2610,68 @@
           <t>sbagliata</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7252</v>
+        <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>7252</v>
+        <v>7251</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>01 04 09 14 16 27 29 47</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>05 06 10 17 20 24 30 36</t>
+          <t>FreqCold8</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>06 11 20 24 32 33</t>
+          <t>05 09 11 14 35 36</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>06 20 24</t>
+          <t>09 14</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I3" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7253</v>
+        <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>7253</v>
+        <v>7252</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>05 10 17 20 28 30 36 49</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>05 06 10 20 24 30 36 46</t>
+          <t>FreqHot8</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>02 05 25 26 27 45</t>
+          <t>06 11 20 24 32 33</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -4195,226 +2682,212 @@
           <t>sbagliata</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>3</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7254</v>
+        <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>7254</v>
+        <v>7253</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>01 04 09 16 26 27 29 47</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>05 06 10 20 24 30 36 46</t>
+          <t>FreqCold8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>06 12 17 20 32 46</t>
+          <t>02 05 25 26 27 45</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>06 20 46</t>
+          <t>26 27</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I5" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>7255</v>
+        <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>7255</v>
+        <v>7254</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>05 10 11 17 20 24 30 36</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>05 06 20 24 30 36 46 49</t>
+          <t>FreqHot8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12 35 36 37 39 40</t>
+          <t>06 12 17 20 32 46</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>17 20</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I6" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>7256</v>
+        <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>7256</v>
+        <v>7255</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>05 06 10 11 17 20 30 36</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>05 06 20 24 30 36 37 46</t>
+          <t>FreqHot8</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>02 05 14 36 40 44</t>
+          <t>12 35 36 37 39 40</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>05 36</t>
+          <t>36</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I7" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7257</v>
+        <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>7257</v>
+        <v>7256</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>05 06 10 11 17 20 30 36</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>05 06 20 24 30 36 37 44</t>
+          <t>FreqHot8</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>10 12 29 37 39 45</t>
+          <t>02 05 14 36 40 44</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>05 36</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I8" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>7258</v>
+        <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>7258</v>
+        <v>7257</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>04 08 10 16 21 28 29 48</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>05 06 20 24 30 36 37 39</t>
+          <t>Delay8</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>03 07 21 27 32 45</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
+          <t>10 12 29 37 39 45</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>10 29</t>
+        </is>
+      </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I9" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>7259</v>
+        <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>7259</v>
+        <v>7258</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>01 04 09 16 27 41 47 48</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>05 06 20 24 30 36 37 39</t>
+          <t>FreqCold8</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>17 18 31 36 42 43</t>
+          <t>03 07 21 27 32 45</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -4425,74 +2898,68 @@
           <t>sbagliata</t>
         </is>
       </c>
-      <c r="I10" t="n">
-        <v>9</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>7260</v>
+        <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>7260</v>
+        <v>7259</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>05 06 10 11 17 20 30 36</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>05 06 20 24 30 36 37 39</t>
+          <t>FreqHot8</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>10 32 34 36 43 45</t>
+          <t>17 18 31 36 42 43</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>17 36</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I11" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>7261</v>
+        <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>7261</v>
+        <v>7260</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>05 06 10 11 17 20 30 36</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>05 06 10 20 24 30 32 36</t>
+          <t>FreqHot8</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>07 15 17 20 36 48</t>
+          <t>10 32 34 36 43 45</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>20 36</t>
+          <t>10 36</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -4503,326 +2970,315 @@
           <t>sbagliata</t>
         </is>
       </c>
-      <c r="I12" t="n">
-        <v>11</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>7262</v>
+        <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>7262</v>
+        <v>7261</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>05 06 10 17 20 30 32 36</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>05 10 20 24 30 32 36 37</t>
+          <t>FreqHot8</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>06 07 17 30 39 49</t>
+          <t>07 15 17 20 36 48</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>17 20 36</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I13" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>7263</v>
+        <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>7263</v>
+        <v>7262</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>05 06 10 17 20 30 32 36</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>05 06 20 24 30 32 36 37</t>
+          <t>FreqHot8</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>04 13 14 16 38 47</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
+          <t>06 07 17 30 39 49</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>06 17 30</t>
+        </is>
+      </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I14" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>7264</v>
+        <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>7264</v>
+        <v>7263</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>01 04 13 16 26 33 41 47</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>05 20 24 30 32 36 39 49</t>
+          <t>Decade8</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>11 15 19 27 28 45</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
+          <t>04 13 14 16 38 47</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>04 13 16 47</t>
+        </is>
+      </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>sbagliata</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>14</v>
+          <t>GIUSTA (4+)</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>7265</v>
+        <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>7265</v>
+        <v>7264</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>01 08 09 19 22 23 28 41</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>05 20 24 30 32 36 39 49</t>
+          <t>Delay8</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>08 11 18 26 45 49</t>
+          <t>11 15 19 27 28 45</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>19 28</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I16" t="n">
-        <v>15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>7266</v>
+        <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>7266</v>
+        <v>7265</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2025-10-25</t>
+          <t>05 06 17 20 30 32 36 49</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>05 11 20 30 32 36 39 49</t>
+          <t>FreqHot8</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>11 20 21 27 39 46</t>
+          <t>08 11 18 26 45 49</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>11 20 39</t>
+          <t>49</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I17" t="n">
-        <v>16</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>7267</v>
+        <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>7267</v>
+        <v>7266</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>05 06 17 20 30 32 36 49</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>05 11 20 30 32 36 39 49</t>
+          <t>FreqHot8</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>18 22 27 31 34 47</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
+          <t>11 20 21 27 39 46</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I18" t="n">
-        <v>17</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>7268</v>
+        <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>7268</v>
+        <v>7267</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>01 04 09 16 26 41 47 48</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>05 11 20 30 32 36 39 49</t>
+          <t>FreqCold8</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>03 10 15 30 31 49</t>
+          <t>18 22 27 31 34 47</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>30 49</t>
+          <t>47</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I19" t="n">
-        <v>18</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>7269</v>
+        <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>7269</v>
+        <v>7268</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>05 06 10 17 20 30 36 49</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>05 11 20 30 32 36 39 49</t>
+          <t>FreqHot8</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>08 14 15 28 40 46</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
+          <t>03 10 15 30 31 49</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>10 30 49</t>
+        </is>
+      </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I20" t="n">
-        <v>19</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>7270</v>
+        <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>7270</v>
+        <v>7269</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>05 06 10 17 20 30 36 49</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>05 11 20 28 30 32 36 39</t>
+          <t>FreqHot8</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>04 23 34 37 45 46</t>
+          <t>08 14 15 28 40 46</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -4834,191 +3290,176 @@
           <t>sbagliata</t>
         </is>
       </c>
-      <c r="I21" t="n">
-        <v>20</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>7271</v>
+        <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>7271</v>
+        <v>7270</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>01 04 09 16 26 41 47 48</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>05 20 30 32 36 37 39 46</t>
+          <t>FreqCold8</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>20 29 33 34 39 42</t>
+          <t>04 23 34 37 45 46</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>20 39</t>
+          <t>04</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I22" t="n">
-        <v>21</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>7272</v>
+        <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>7272</v>
+        <v>7271</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>01 09 16 26 29 33 47 48</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>05 20 30 32 36 37 39 46</t>
+          <t>Decade8</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>07 10 20 30 35 39</t>
+          <t>20 29 33 34 39 42</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>20 30 39</t>
+          <t>29 33</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I23" t="n">
-        <v>22</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>7273</v>
+        <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>7273</v>
+        <v>7272</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>05 06 10 17 20 30 36 46</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>05 20 30 36 37 39 46 49</t>
+          <t>FreqHot8</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>01 05 14 26 46 47</t>
+          <t>07 10 20 30 35 39</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>05 46</t>
+          <t>10 20 30</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I24" t="n">
-        <v>23</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>7274</v>
+        <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>7274</v>
+        <v>7273</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>01 04 09 16 26 41 47 48</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>05 20 30 36 37 39 46 49</t>
+          <t>FreqCold8</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>01 18 31 37 42 43</t>
+          <t>01 05 14 26 46 47</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>01 26 47</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I25" t="n">
-        <v>24</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>7275</v>
+        <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>7275</v>
+        <v>7274</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>01 04 09 16 26 41 47 48</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>05 20 30 36 37 39 46 49</t>
+          <t>FreqCold8</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>02 12 19 32 39 44</t>
+          <t>01 18 31 37 42 43</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>01</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5029,143 +3470,135 @@
           <t>sbagliata</t>
         </is>
       </c>
-      <c r="I26" t="n">
-        <v>25</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>7276</v>
+        <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>7276</v>
+        <v>7275</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>02 09 12 24 25 32 41 44</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>05 20 30 32 36 37 39 46</t>
+          <t>Delay8</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>07 13 22 30 38 39</t>
+          <t>02 12 19 32 39 44</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>30 39</t>
+          <t>02 12 32 44</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>sbagliata</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>26</v>
+          <t>GIUSTA (4+)</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>7277</v>
+        <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>7277</v>
+        <v>7276</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>05 06 20 30 36 37 39 46</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>05 20 30 32 36 37 39 46</t>
+          <t>FreqHot8</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>09 19 20 22 27 44</t>
+          <t>07 13 22 30 38 39</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30 39</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I28" t="n">
-        <v>27</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>7278</v>
+        <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>7278</v>
+        <v>7277</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>04 09 16 20 30 36 39 48</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>05 20 30 32 36 37 39 46</t>
+          <t>HotCold4+4</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>08 22 31 43 45 49</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
+          <t>09 19 20 22 27 44</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>09 20</t>
+        </is>
+      </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I29" t="n">
-        <v>28</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>7279</v>
+        <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>7279</v>
+        <v>7278</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>05 06 10 20 30 36 39 46</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>05 20 30 32 36 37 39 49</t>
+          <t>FreqHot8</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>03 09 26 31 42 44</t>
+          <t>08 22 31 43 45 49</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
@@ -5177,105 +3610,104 @@
           <t>sbagliata</t>
         </is>
       </c>
-      <c r="I30" t="n">
-        <v>29</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>7280</v>
+        <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>7280</v>
+        <v>7279</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>04 09 16 26 29 41 47 48</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>05 20 30 32 36 39 46 49</t>
+          <t>FreqCold8</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>27 33 38 43 45 47</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
+          <t>03 09 26 31 42 44</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>09 26</t>
+        </is>
+      </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I31" t="n">
-        <v>30</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>7281</v>
+        <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>7281</v>
+        <v>7280</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>04 09 16 26 29 41 47 48</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>05 20 30 32 36 39 43 49</t>
+          <t>FreqCold8</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>03 23 28 31 42 46</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
+          <t>27 33 38 43 45 47</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I32" t="n">
-        <v>31</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>7282</v>
+        <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>7282</v>
+        <v>7281</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>05 10 20 30 36 39 46 49</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>05 20 28 30 31 36 46 49</t>
+          <t>FreqHot8</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>03 09 29 30 32 47</t>
+          <t>03 23 28 31 42 46</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>46</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5286,74 +3718,68 @@
           <t>sbagliata</t>
         </is>
       </c>
-      <c r="I33" t="n">
-        <v>32</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>7283</v>
+        <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>7283</v>
+        <v>7282</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>04 09 16 26 29 41 47 48</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>05 20 28 30 32 36 39 46</t>
+          <t>FreqCold8</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>21 23 32 45 46 47</t>
+          <t>03 09 29 30 32 47</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>32 46</t>
+          <t>09 29 47</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I34" t="n">
-        <v>33</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>7284</v>
+        <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>7284</v>
+        <v>7283</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>05 20 30 31 36 39 46 49</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>20 28 30 32 36 39 43 46</t>
+          <t>FreqHot8</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>04 14 25 27 43 44</t>
+          <t>21 23 32 45 46 47</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>46</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5364,144 +3790,140 @@
           <t>sbagliata</t>
         </is>
       </c>
-      <c r="I35" t="n">
-        <v>34</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>7285</v>
+        <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>7285</v>
+        <v>7284</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>01 04 16 26 29 40 41 48</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>20 30 32 36 39 43 45 46</t>
+          <t>FreqCold8</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>02 10 22 26 31 40</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
+          <t>04 14 25 27 43 44</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I36" t="n">
-        <v>35</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>7286</v>
+        <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>7286</v>
+        <v>7285</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>01 04 16 26 29 40 41 48</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>20 30 31 32 36 39 43 46</t>
+          <t>FreqCold8</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>01 05 11 38 42 46</t>
+          <t>02 10 22 26 31 40</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>26 40</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I37" t="n">
-        <v>36</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>7287</v>
+        <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>7287</v>
+        <v>7286</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>05 20 30 32 36 39 46 49</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>05 20 30 32 36 39 43 46</t>
+          <t>FreqHot8</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>03 10 14 45 47 49</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
+          <t>01 05 11 38 42 46</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>05 46</t>
+        </is>
+      </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I38" t="n">
-        <v>37</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>7288</v>
+        <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>7288</v>
+        <v>7287</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>05 20 30 32 36 39 46 49</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>20 30 32 36 39 43 45 46</t>
+          <t>FreqHot8</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>17 25 26 27 32 37</t>
+          <t>03 10 14 45 47 49</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>49</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5512,339 +3934,320 @@
           <t>sbagliata</t>
         </is>
       </c>
-      <c r="I39" t="n">
-        <v>38</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>7289</v>
+        <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>7289</v>
+        <v>7288</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>05 20 30 32 36 39 46 49</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>05 30 32 36 39 43 45 46</t>
+          <t>FreqHot8</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>10 20 26 33 37 38</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr"/>
+          <t>17 25 26 27 32 37</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I40" t="n">
-        <v>39</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>7290</v>
+        <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>7290</v>
+        <v>7289</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>05 20 30 31 32 36 39 46</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>05 30 32 36 39 43 45 46</t>
+          <t>FreqHot8</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>04 06 11 16 24 41</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr"/>
+          <t>10 20 26 33 37 38</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I41" t="n">
-        <v>40</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>7291</v>
+        <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>7291</v>
+        <v>7290</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>06 15 16 24 34 36 41 48</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>05 11 30 32 36 43 45 46</t>
+          <t>Delay8</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>03 09 36 39 43 47</t>
+          <t>04 06 11 16 24 41</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>36 43</t>
+          <t>06 16 24 41</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>sbagliata</t>
-        </is>
-      </c>
-      <c r="I42" t="n">
-        <v>41</v>
+          <t>GIUSTA (4+)</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>7292</v>
+        <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>7292</v>
+        <v>7291</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2025-12-25</t>
+          <t>05 20 30 32 36 37 39 46</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>05 30 32 36 39 43 45 46</t>
+          <t>FreqHot8</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>14 19 20 45 48 49</t>
+          <t>03 09 36 39 43 47</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>36 39</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I43" t="n">
-        <v>42</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>7293</v>
+        <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>7293</v>
+        <v>7292</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>16 20 29 32 36 39 41 48</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>05 30 32 36 39 43 45 46</t>
+          <t>HotCold4+4</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>09 26 31 40 45 48</t>
+          <t>14 19 20 45 48 49</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>20 48</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I44" t="n">
-        <v>43</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>7294</v>
+        <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>7294</v>
+        <v>7293</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>01 04 09 16 29 40 41 48</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>11 30 32 36 39 43 45 46</t>
+          <t>FreqCold8</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>01 06 15 26 29 30</t>
+          <t>09 26 31 40 45 48</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>09 40 48</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I45" t="n">
-        <v>44</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>7295</v>
+        <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>7295</v>
+        <v>7294</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>01 04 08 16 29 40 41 48</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>11 30 32 36 39 43 45 46</t>
+          <t>FreqCold8</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>25 26 32 38 39 46</t>
+          <t>01 06 15 26 29 30</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>32 39 46</t>
+          <t>01 29</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I46" t="n">
-        <v>45</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>7296</v>
+        <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>7296</v>
+        <v>7295</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-01-03</t>
+          <t>20 30 31 32 37 39 45 46</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>11 30 32 36 39 43 45 46</t>
+          <t>FreqHot8</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>07 10 21 22 42 45</t>
+          <t>25 26 32 38 39 46</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>32 39 46</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I47" t="n">
-        <v>46</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>7297</v>
+        <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>7297</v>
+        <v>7296</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>20 30 32 37 39 45 46 49</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>11 14 30 32 39 43 45 46</t>
+          <t>FreqHot8</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>09 10 14 26 28 47</t>
+          <t>07 10 21 22 42 45</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>45</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -5855,183 +4258,176 @@
           <t>sbagliata</t>
         </is>
       </c>
-      <c r="I48" t="n">
-        <v>47</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>7298</v>
+        <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>7298</v>
+        <v>7297</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>08 12 13 18 23 28 34 35</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>10 14 30 32 39 43 45 46</t>
+          <t>Delay8</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>09 12 21 25 44 48</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr"/>
+          <t>09 10 14 26 28 47</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I49" t="n">
-        <v>48</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>7299</v>
+        <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>7299</v>
+        <v>7298</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>08 12 13 18 23 34 35 44</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>10 14 30 32 39 43 45 46</t>
+          <t>Delay8</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>03 04 07 08 14 26</t>
+          <t>09 12 21 25 44 48</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12 44</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I50" t="n">
-        <v>49</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>7300</v>
+        <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>7300</v>
+        <v>7299</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>01 04 08 16 29 40 41 48</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>03 14 30 32 39 43 45 46</t>
+          <t>FreqCold8</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>07 13 21 29 31 36</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr"/>
+          <t>03 04 07 08 14 26</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>04 08</t>
+        </is>
+      </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I51" t="n">
-        <v>50</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>7301</v>
+        <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>7301</v>
+        <v>7300</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>01 04 08 16 29 40 41 48</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>14 30 32 36 39 43 45 46</t>
+          <t>FreqCold8</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>08 15 23 43 45 47</t>
+          <t>07 13 21 29 31 36</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>43 45</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I52" t="n">
-        <v>51</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>7302</v>
+        <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>7302</v>
+        <v>7301</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>10 30 31 32 36 45 46 49</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>14 30 32 36 39 43 45 46</t>
+          <t>FreqHot8</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>01 03 06 12 13 14</t>
+          <t>08 15 23 43 45 47</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>45</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6042,109 +4438,104 @@
           <t>sbagliata</t>
         </is>
       </c>
-      <c r="I53" t="n">
-        <v>52</v>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>7303</v>
+        <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>7303</v>
+        <v>7302</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>01 04 16 18 29 40 41 48</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>03 12 14 30 32 43 45 46</t>
+          <t>FreqCold8</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>05 10 12 30 37 48</t>
+          <t>01 03 06 12 13 14</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>12 30</t>
+          <t>01</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I54" t="n">
-        <v>53</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>7304</v>
+        <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>7304</v>
+        <v>7303</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>10 14 30 32 36 43 45 46</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>03 12 14 30 32 43 45 46</t>
+          <t>FreqHot8</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>01 05 15 25 44 49</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr"/>
+          <t>05 10 12 30 37 48</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>10 30</t>
+        </is>
+      </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I55" t="n">
-        <v>54</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>7305</v>
+        <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>7305</v>
+        <v>7304</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>01 04 16 18 29 40 41 48</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>03 12 14 30 32 43 45 46</t>
+          <t>FreqCold8</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>06 11 13 21 25 43</t>
+          <t>01 05 15 25 44 49</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>01</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -6155,70 +4546,68 @@
           <t>sbagliata</t>
         </is>
       </c>
-      <c r="I56" t="n">
-        <v>55</v>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>7306</v>
+        <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>7306</v>
+        <v>7305</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>05 14 30 32 36 43 45 46</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>03 12 14 30 32 43 45 46</t>
+          <t>FreqHot8</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>05 08 11 31 42 48</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr"/>
+          <t>06 11 13 21 25 43</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I57" t="n">
-        <v>56</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>7307</v>
+        <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>7307</v>
+        <v>7306</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>05 10 14 30 32 43 45 46</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>03 12 14 30 32 43 45 46</t>
+          <t>FreqHot8</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>02 06 12 24 31 36</t>
+          <t>05 08 11 31 42 48</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>05</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -6229,35 +4618,32 @@
           <t>sbagliata</t>
         </is>
       </c>
-      <c r="I58" t="n">
-        <v>57</v>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>7308</v>
+        <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>7308</v>
+        <v>7307</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>01 02 04 16 29 40 41 48</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>03 12 14 30 32 43 45 46</t>
+          <t>FreqCold8</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>06 08 14 22 34 40</t>
+          <t>02 06 12 24 31 36</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>02</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -6268,35 +4654,32 @@
           <t>sbagliata</t>
         </is>
       </c>
-      <c r="I59" t="n">
-        <v>58</v>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>7309</v>
+        <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>7309</v>
+        <v>7308</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>01 02 04 16 29 40 41 48</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>03 12 14 30 32 43 45 46</t>
+          <t>FreqCold8</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>01 21 25 27 32 47</t>
+          <t>06 08 14 22 34 40</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>40</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -6307,35 +4690,32 @@
           <t>sbagliata</t>
         </is>
       </c>
-      <c r="I60" t="n">
-        <v>59</v>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>7310</v>
+        <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>7310</v>
+        <v>7309</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>14 30 31 32 36 43 45 46</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>03 12 14 30 32 43 45 46</t>
+          <t>FreqHot8</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>03 07 08 09 24 42</t>
+          <t>01 21 25 27 32 47</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -6346,222 +4726,208 @@
           <t>sbagliata</t>
         </is>
       </c>
-      <c r="I61" t="n">
-        <v>60</v>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>7311</v>
+        <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>7311</v>
+        <v>7310</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>05 14 30 32 36 43 45 46</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>03 12 14 30 32 43 45 46</t>
+          <t>FreqHot8</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>02 10 19 25 30 36</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>03 07 08 09 24 42</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I62" t="n">
-        <v>61</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>7312</v>
+        <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>7312</v>
+        <v>7311</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>05 14 30 32 36 43 45 46</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>03 12 14 30 32 36 43 45</t>
+          <t>FreqHot8</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>05 12 13 16 23 24</t>
+          <t>02 10 19 25 30 36</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>30 36</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I63" t="n">
-        <v>62</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>7313</v>
+        <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>7313</v>
+        <v>7312</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>01 04 16 18 23 29 35 41</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>03 12 14 30 31 32 36 45</t>
+          <t>Decade8</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>11 16 33 39 42 44</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr"/>
+          <t>05 12 13 16 23 24</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>16 23</t>
+        </is>
+      </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I64" t="n">
-        <v>63</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>7314</v>
+        <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>7314</v>
+        <v>7313</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>17 18 20 33 35 38 39 41</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>03 12 14 30 32 36 43 45</t>
+          <t>Delay8</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>01 19 26 32 38 41</t>
+          <t>11 16 33 39 42 44</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33 39</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I65" t="n">
-        <v>64</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>7315</v>
+        <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>7315</v>
+        <v>7314</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>01 04 16 29 35 40 41 48</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>03 12 14 30 32 36 43 45</t>
+          <t>FreqCold8</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>09 22 23 26 39 49</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr"/>
+          <t>01 19 26 32 38 41</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>01 41</t>
+        </is>
+      </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I66" t="n">
-        <v>65</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>7316</v>
+        <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>7316</v>
+        <v>7315</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>01 04 16 18 23 29 35 48</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>03 12 14 30 32 36 43 45</t>
+          <t>Decade8</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>02 05 13 14 15 39</t>
+          <t>09 22 23 26 39 49</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -6572,335 +4938,320 @@
           <t>sbagliata</t>
         </is>
       </c>
-      <c r="I67" t="n">
-        <v>66</v>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>7317</v>
+        <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>7317</v>
+        <v>7316</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>12 14 30 32 36 39 43 45</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>03 12 14 30 32 36 39 45</t>
+          <t>FreqHot8</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>02 12 14 21 39 49</t>
+          <t>02 05 13 14 15 39</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>12 14 39</t>
+          <t>14 39</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I68" t="n">
-        <v>67</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>7318</v>
+        <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>7318</v>
+        <v>7317</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>05 12 14 30 32 39 43 45</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>03 12 14 30 32 36 39 45</t>
+          <t>FreqHot8</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>09 13 17 25 31 41</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr"/>
+          <t>02 12 14 21 39 49</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>12 14 39</t>
+        </is>
+      </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I69" t="n">
-        <v>68</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>7319</v>
+        <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>7319</v>
+        <v>7318</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>04 16 18 29 35 40 41 48</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>03 12 14 30 31 32 39 45</t>
+          <t>FreqCold8</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>08 09 13 15 38 48</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr"/>
+          <t>09 13 17 25 31 41</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I70" t="n">
-        <v>69</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>7320</v>
+        <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>7320</v>
+        <v>7319</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>04 16 18 29 35 40 41 48</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>12 14 30 31 32 36 39 45</t>
+          <t>FreqCold8</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>04 09 10 28 40 48</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr"/>
+          <t>08 09 13 15 38 48</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I71" t="n">
-        <v>70</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>7321</v>
+        <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>7321</v>
+        <v>7320</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>04 16 18 29 35 40 41 48</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>10 12 14 30 31 32 39 45</t>
+          <t>FreqCold8</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>05 09 10 12 13 42</t>
+          <t>04 09 10 28 40 48</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>10 12</t>
+          <t>04 40 48</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I72" t="n">
-        <v>71</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>7322</v>
+        <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>7322</v>
+        <v>7321</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>10 12 13 14 30 32 39 45</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>09 10 12 13 14 32 39 45</t>
+          <t>FreqHot8</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>05 20 33 41 42 45</t>
+          <t>05 09 10 12 13 42</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>10 12 13</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I73" t="n">
-        <v>72</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>7323</v>
+        <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>7323</v>
+        <v>7322</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>18 20 29 35 37 43 45 46</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>09 10 12 13 14 32 39 45</t>
+          <t>Delay8</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>02 07 10 18 27 29</t>
+          <t>05 20 33 41 42 45</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20 45</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I74" t="n">
-        <v>73</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>7324</v>
+        <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>7324</v>
+        <v>7323</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>04 16 18 29 35 40 41 48</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>09 10 12 14 30 32 39 45</t>
+          <t>FreqCold8</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>03 12 26 36 37 38</t>
+          <t>02 07 10 18 27 29</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18 29</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I75" t="n">
-        <v>74</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>7325</v>
+        <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>7325</v>
+        <v>7324</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>03 06 34 35 37 43 46 47</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>03 10 12 14 32 36 39 45</t>
+          <t>Delay8</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>05 06 10 15 36 42</t>
+          <t>03 12 26 36 37 38</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>10 36</t>
+          <t>03 37</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -6911,179 +5262,176 @@
           <t>sbagliata</t>
         </is>
       </c>
-      <c r="I76" t="n">
-        <v>75</v>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>7326</v>
+        <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>7326</v>
+        <v>7325</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>06 24 30 34 35 43 46 47</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>03 05 10 12 14 32 36 45</t>
+          <t>Delay8</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>22 23 30 41 46 47</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr"/>
+          <t>05 06 10 15 36 42</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I77" t="n">
-        <v>76</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>7327</v>
+        <v>77</v>
       </c>
       <c r="B78" t="n">
-        <v>7327</v>
+        <v>7326</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>11 24 30 34 35 43 46 47</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>03 10 12 14 30 32 36 45</t>
+          <t>Delay8</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>06 07 16 18 37 41</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr"/>
+          <t>22 23 30 41 46 47</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>30 46 47</t>
+        </is>
+      </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I78" t="n">
-        <v>77</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>7328</v>
+        <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>7328</v>
+        <v>7327</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>01 04 16 18 29 35 40 48</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>03 05 10 12 14 30 36 45</t>
+          <t>FreqCold8</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>01 02 19 25 36 43</t>
+          <t>06 07 16 18 37 41</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>16 18</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I79" t="n">
-        <v>78</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>7329</v>
+        <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>7329</v>
+        <v>7328</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>01 11 19 24 34 35 43 44</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>03 05 10 12 14 30 36 45</t>
+          <t>Delay8</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>21 22 25 40 47 49</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr"/>
+          <t>01 02 19 25 36 43</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>01 19 43</t>
+        </is>
+      </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I80" t="n">
-        <v>79</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>7330</v>
+        <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>7330</v>
+        <v>7329</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>01 04 16 18 29 35 40 48</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>03 05 06 10 14 30 36 45</t>
+          <t>FreqCold8</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>09 13 16 17 38 45</t>
+          <t>21 22 25 40 47 49</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>40</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -7094,113 +5442,104 @@
           <t>sbagliata</t>
         </is>
       </c>
-      <c r="I81" t="n">
-        <v>80</v>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>7331</v>
+        <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>7331</v>
+        <v>7330</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>10 12 14 30 32 36 43 45</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>03 05 06 09 10 14 36 45</t>
+          <t>FreqHot8</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>10 12 16 27 36 40</t>
+          <t>09 13 16 17 38 45</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>10 36</t>
+          <t>45</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I82" t="n">
-        <v>81</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>7332</v>
+        <v>82</v>
       </c>
       <c r="B83" t="n">
-        <v>7332</v>
+        <v>7331</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>04 10 12 14 16 29 35 36</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>03 06 09 10 12 14 36 45</t>
+          <t>HotCold4+4</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>06 08 14 27 29 30</t>
+          <t>10 12 16 27 36 40</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>06 14</t>
+          <t>10 12 16 36</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>sbagliata</t>
-        </is>
-      </c>
-      <c r="I83" t="n">
-        <v>82</v>
+          <t>GIUSTA (4+)</t>
+        </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>7333</v>
+        <v>83</v>
       </c>
       <c r="B84" t="n">
-        <v>7333</v>
+        <v>7332</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>01 04 08 16 18 29 35 48</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>03 06 09 10 12 14 36 45</t>
+          <t>FreqCold8</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>03 20 26 37 45 47</t>
+          <t>06 08 14 27 29 30</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>03 45</t>
+          <t>08 29</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -7211,35 +5550,32 @@
           <t>sbagliata</t>
         </is>
       </c>
-      <c r="I84" t="n">
-        <v>83</v>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>7334</v>
+        <v>84</v>
       </c>
       <c r="B85" t="n">
-        <v>7334</v>
+        <v>7333</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>03 10 12 13 14 32 36 45</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>03 06 10 12 14 26 36 45</t>
+          <t>FreqHot8</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>05 10 14 33 34 47</t>
+          <t>03 20 26 37 45 47</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>10 14</t>
+          <t>03 45</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -7250,113 +5586,104 @@
           <t>sbagliata</t>
         </is>
       </c>
-      <c r="I85" t="n">
-        <v>84</v>
-      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>7335</v>
+        <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>7335</v>
+        <v>7334</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>03 10 12 13 14 32 36 45</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>06 10 14 26 27 36 45 47</t>
+          <t>FreqHot8</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>03 06 12 26 27 49</t>
+          <t>05 10 14 33 34 47</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>06 26 27</t>
+          <t>10 14</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I86" t="n">
-        <v>85</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>7336</v>
+        <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>7336</v>
+        <v>7335</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>03 10 12 13 14 32 36 45</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>06 10 12 14 26 27 36 45</t>
+          <t>FreqHot8</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>03 06 28 31 33 46</t>
+          <t>03 06 12 26 27 49</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>03 12</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I87" t="n">
-        <v>86</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>7337</v>
+        <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>7337</v>
+        <v>7336</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>03 06 10 12 13 14 36 45</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>03 06 10 14 26 27 36 45</t>
+          <t>FreqHot8</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>03 08 10 23 44 46</t>
+          <t>03 06 28 31 33 46</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>03 10</t>
+          <t>03 06</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -7367,74 +5694,68 @@
           <t>sbagliata</t>
         </is>
       </c>
-      <c r="I88" t="n">
-        <v>87</v>
-      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>7338</v>
+        <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>7338</v>
+        <v>7337</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>03 06 10 12 13 14 36 45</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>03 06 10 14 26 27 36 45</t>
+          <t>FreqHot8</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>16 22 25 31 32 36</t>
+          <t>03 08 10 23 44 46</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>03 10</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I89" t="n">
-        <v>88</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>7339</v>
+        <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>7339</v>
+        <v>7338</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>03 06 10 12 13 14 36 45</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>06 10 14 26 27 31 36 45</t>
+          <t>FreqHot8</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>03 12 14 17 47 49</t>
+          <t>16 22 25 31 32 36</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>36</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -7445,70 +5766,68 @@
           <t>sbagliata</t>
         </is>
       </c>
-      <c r="I90" t="n">
-        <v>89</v>
-      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>7340</v>
+        <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>7340</v>
+        <v>7339</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>03 06 10 12 14 32 36 45</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>03 06 10 14 26 31 36 45</t>
+          <t>FreqHot8</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>21 22 25 27 29 37</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr"/>
+          <t>03 12 14 17 47 49</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>03 12 14</t>
+        </is>
+      </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I91" t="n">
-        <v>90</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>7341</v>
+        <v>91</v>
       </c>
       <c r="B92" t="n">
-        <v>7341</v>
+        <v>7340</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>01 04 16 18 29 35 41 48</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>03 06 10 14 26 27 31 45</t>
+          <t>FreqCold8</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>01 06 19 32 37 43</t>
+          <t>21 22 25 27 29 37</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -7519,292 +5838,284 @@
           <t>sbagliata</t>
         </is>
       </c>
-      <c r="I92" t="n">
-        <v>91</v>
-      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>7342</v>
+        <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>7342</v>
+        <v>7341</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>01 04 16 18 19 35 41 48</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>03 06 10 14 26 27 31 45</t>
+          <t>FreqCold8</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>04 16 38 43 47 49</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr"/>
+          <t>01 06 19 32 37 43</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>01 19</t>
+        </is>
+      </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I93" t="n">
-        <v>92</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>7343</v>
+        <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>7343</v>
+        <v>7342</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>04 16 18 24 29 35 41 48</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>03 06 10 14 26 27 45 47</t>
+          <t>FreqCold8</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>05 09 11 21 27 31</t>
+          <t>04 16 38 43 47 49</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>04 16</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I94" t="n">
-        <v>93</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>7344</v>
+        <v>94</v>
       </c>
       <c r="B95" t="n">
-        <v>7344</v>
+        <v>7343</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>07 11 15 24 35 39 42 48</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>06 10 14 26 27 31 45 47</t>
+          <t>Delay8</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>13 19 20 23 34 41</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr"/>
+          <t>05 09 11 21 27 31</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I95" t="n">
-        <v>94</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>7345</v>
+        <v>95</v>
       </c>
       <c r="B96" t="n">
-        <v>7345</v>
+        <v>7344</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>04 16 18 24 29 35 41 48</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>03 06 10 14 26 27 31 45</t>
+          <t>FreqCold8</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>01 05 21 40 43 44</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr"/>
+          <t>13 19 20 23 34 41</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I96" t="n">
-        <v>95</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>7346</v>
+        <v>96</v>
       </c>
       <c r="B97" t="n">
-        <v>7346</v>
+        <v>7345</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>01 04 16 28 29 35 41 48</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>03 05 06 10 14 26 31 45</t>
+          <t>Decade8</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>03 06 16 30 38 41</t>
+          <t>01 05 21 40 43 44</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>03 06</t>
+          <t>01</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I97" t="n">
-        <v>96</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>7347</v>
+        <v>97</v>
       </c>
       <c r="B98" t="n">
-        <v>7347</v>
+        <v>7346</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>03 05 06 10 12 14 36 45</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>03 05 06 10 14 26 27 45</t>
+          <t>FreqHot8</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>07 15 24 28 32 34</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr"/>
+          <t>03 06 16 30 38 41</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>03 06</t>
+        </is>
+      </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I98" t="n">
-        <v>97</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>7348</v>
+        <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>7348</v>
+        <v>7347</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>07 15 18 24 35 39 42 48</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>03 05 06 10 14 26 27 45</t>
+          <t>Delay8</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>08 15 16 26 33 38</t>
+          <t>07 15 24 28 32 34</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>07 15 24</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
-      </c>
-      <c r="I99" t="n">
-        <v>98</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>7349</v>
+        <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>7349</v>
+        <v>7348</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>04 16 18 28 29 35 41 48</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>03 05 06 10 14 26 45 47</t>
+          <t>FreqCold8</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>24 25 33 36 40 45</t>
+          <t>08 15 16 26 33 38</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>16</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -7815,51 +6126,49 @@
           <t>sbagliata</t>
         </is>
       </c>
-      <c r="I100" t="n">
-        <v>99</v>
-      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>7350</v>
+        <v>100</v>
       </c>
       <c r="B101" t="n">
-        <v>7350</v>
+        <v>7349</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>03 05 06 10 12 14 36 45</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>03 05 06 10 14 26 45 47</t>
+          <t>FreqHot8</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>01 02 08 28 35 47</t>
+          <t>24 25 33 36 40 45</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>36 45</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
           <t>sbagliata</t>
         </is>
       </c>
-      <c r="I101" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr"/>
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>STASERA</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>?</t>
@@ -7867,12 +6176,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>stasera</t>
+          <t>03 04 14 18 35 48</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>06 14 20 30 36 45</t>
+          <t>consenso 8 strategie</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -7882,7 +6191,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>← L'ULTIMA ALL'APPELLO</t>
+          <t>← UNO DEI 0 POSTI ALL'APPELLO</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -7892,12 +6201,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>FORZATA PER ESCLUSIONE</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>STASERA</t>
+          <t>CANDIDATA PER ESCLUSIONE</t>
         </is>
       </c>
     </row>
